--- a/public/templates/BF_Prime_Drivers_template.xlsx
+++ b/public/templates/BF_Prime_Drivers_template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
   <si>
     <t xml:space="preserve">Statement # </t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t xml:space="preserve">Truck insurance </t>
+  </si>
+  <si>
+    <t>`</t>
   </si>
   <si>
     <t>Fuel:</t>
@@ -674,7 +677,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="103">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -920,6 +923,9 @@
     </xf>
     <xf borderId="20" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="22" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -1247,9 +1253,7 @@
       <c r="E3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="5">
-        <v>24209.0</v>
-      </c>
+      <c r="F3" s="5"/>
       <c r="G3" s="6"/>
       <c r="H3" s="1"/>
       <c r="I3" s="7" t="s">
@@ -1267,9 +1271,7 @@
       <c r="E4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="11">
-        <v>45981.0</v>
-      </c>
+      <c r="F4" s="11"/>
       <c r="G4" s="12"/>
       <c r="H4" s="1"/>
       <c r="I4" s="13" t="s">
@@ -1961,7 +1963,9 @@
     <row r="45" ht="21.0" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
+      <c r="C45" s="84" t="s">
+        <v>31</v>
+      </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -1974,7 +1978,7 @@
     </row>
     <row r="46" ht="21.0" customHeight="1">
       <c r="A46" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B46" s="51"/>
       <c r="C46" s="1"/>
@@ -1989,302 +1993,302 @@
       <c r="L46" s="1"/>
     </row>
     <row r="47" ht="21.0" customHeight="1">
-      <c r="A47" s="84" t="s">
-        <v>32</v>
-      </c>
-      <c r="B47" s="85" t="s">
+      <c r="A47" s="85" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="C47" s="84" t="s">
-        <v>33</v>
-      </c>
-      <c r="D47" s="84" t="s">
+      <c r="C47" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="84" t="s">
+      <c r="D47" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="F47" s="84" t="s">
+      <c r="E47" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="G47" s="84" t="s">
+      <c r="F47" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="H47" s="86" t="s">
+      <c r="G47" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="I47" s="87" t="s">
+      <c r="H47" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="J47" s="88" t="s">
+      <c r="I47" s="88" t="s">
+        <v>40</v>
+      </c>
+      <c r="J47" s="89" t="s">
         <v>22</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
     </row>
     <row r="48" ht="21.0" customHeight="1">
-      <c r="A48" s="89"/>
-      <c r="B48" s="89"/>
-      <c r="C48" s="89"/>
-      <c r="D48" s="89"/>
-      <c r="E48" s="89"/>
-      <c r="F48" s="90"/>
-      <c r="G48" s="89"/>
-      <c r="H48" s="91"/>
-      <c r="I48" s="92"/>
-      <c r="J48" s="93"/>
+      <c r="A48" s="90"/>
+      <c r="B48" s="90"/>
+      <c r="C48" s="90"/>
+      <c r="D48" s="90"/>
+      <c r="E48" s="90"/>
+      <c r="F48" s="91"/>
+      <c r="G48" s="90"/>
+      <c r="H48" s="92"/>
+      <c r="I48" s="93"/>
+      <c r="J48" s="94"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
     </row>
     <row r="49" ht="21.0" customHeight="1">
-      <c r="A49" s="89"/>
-      <c r="B49" s="89"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="89"/>
-      <c r="E49" s="89"/>
-      <c r="F49" s="90"/>
-      <c r="G49" s="89"/>
-      <c r="H49" s="91"/>
-      <c r="I49" s="94"/>
-      <c r="J49" s="95"/>
+      <c r="A49" s="90"/>
+      <c r="B49" s="90"/>
+      <c r="C49" s="90"/>
+      <c r="D49" s="90"/>
+      <c r="E49" s="90"/>
+      <c r="F49" s="91"/>
+      <c r="G49" s="90"/>
+      <c r="H49" s="92"/>
+      <c r="I49" s="95"/>
+      <c r="J49" s="96"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
     </row>
     <row r="50" ht="21.0" customHeight="1">
-      <c r="A50" s="89"/>
-      <c r="B50" s="89"/>
-      <c r="C50" s="89"/>
-      <c r="D50" s="89"/>
-      <c r="E50" s="89"/>
-      <c r="F50" s="90"/>
-      <c r="G50" s="89"/>
-      <c r="H50" s="91"/>
-      <c r="I50" s="96"/>
-      <c r="J50" s="95"/>
+      <c r="A50" s="90"/>
+      <c r="B50" s="90"/>
+      <c r="C50" s="90"/>
+      <c r="D50" s="90"/>
+      <c r="E50" s="90"/>
+      <c r="F50" s="91"/>
+      <c r="G50" s="90"/>
+      <c r="H50" s="92"/>
+      <c r="I50" s="97"/>
+      <c r="J50" s="96"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
     </row>
     <row r="51" ht="21.0" customHeight="1">
-      <c r="A51" s="89"/>
-      <c r="B51" s="89"/>
-      <c r="C51" s="89"/>
-      <c r="D51" s="89"/>
-      <c r="E51" s="89"/>
-      <c r="F51" s="90"/>
-      <c r="G51" s="89"/>
-      <c r="H51" s="91"/>
-      <c r="I51" s="97"/>
-      <c r="J51" s="98"/>
+      <c r="A51" s="90"/>
+      <c r="B51" s="90"/>
+      <c r="C51" s="90"/>
+      <c r="D51" s="90"/>
+      <c r="E51" s="90"/>
+      <c r="F51" s="91"/>
+      <c r="G51" s="90"/>
+      <c r="H51" s="92"/>
+      <c r="I51" s="98"/>
+      <c r="J51" s="99"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
     </row>
     <row r="52" ht="21.0" customHeight="1">
-      <c r="A52" s="89"/>
-      <c r="B52" s="89"/>
-      <c r="C52" s="89"/>
-      <c r="D52" s="89"/>
-      <c r="E52" s="89"/>
-      <c r="F52" s="90"/>
-      <c r="G52" s="89"/>
-      <c r="H52" s="91"/>
-      <c r="I52" s="94"/>
-      <c r="J52" s="95"/>
+      <c r="A52" s="90"/>
+      <c r="B52" s="90"/>
+      <c r="C52" s="90"/>
+      <c r="D52" s="90"/>
+      <c r="E52" s="90"/>
+      <c r="F52" s="91"/>
+      <c r="G52" s="90"/>
+      <c r="H52" s="92"/>
+      <c r="I52" s="95"/>
+      <c r="J52" s="96"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
     </row>
     <row r="53" ht="21.0" customHeight="1">
-      <c r="A53" s="89"/>
-      <c r="B53" s="89"/>
-      <c r="C53" s="89"/>
-      <c r="D53" s="89"/>
-      <c r="E53" s="89"/>
-      <c r="F53" s="90"/>
-      <c r="G53" s="89"/>
-      <c r="H53" s="91"/>
-      <c r="I53" s="94"/>
-      <c r="J53" s="95"/>
+      <c r="A53" s="90"/>
+      <c r="B53" s="90"/>
+      <c r="C53" s="90"/>
+      <c r="D53" s="90"/>
+      <c r="E53" s="90"/>
+      <c r="F53" s="91"/>
+      <c r="G53" s="90"/>
+      <c r="H53" s="92"/>
+      <c r="I53" s="95"/>
+      <c r="J53" s="96"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
     </row>
     <row r="54" ht="21.0" customHeight="1">
-      <c r="A54" s="89"/>
-      <c r="B54" s="89"/>
-      <c r="C54" s="89"/>
-      <c r="D54" s="89"/>
-      <c r="E54" s="89"/>
-      <c r="F54" s="90"/>
-      <c r="G54" s="89"/>
-      <c r="H54" s="91"/>
-      <c r="I54" s="96"/>
-      <c r="J54" s="95"/>
+      <c r="A54" s="90"/>
+      <c r="B54" s="90"/>
+      <c r="C54" s="90"/>
+      <c r="D54" s="90"/>
+      <c r="E54" s="90"/>
+      <c r="F54" s="91"/>
+      <c r="G54" s="90"/>
+      <c r="H54" s="92"/>
+      <c r="I54" s="97"/>
+      <c r="J54" s="96"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
     </row>
     <row r="55" ht="21.0" customHeight="1">
-      <c r="A55" s="89"/>
-      <c r="B55" s="89"/>
-      <c r="C55" s="89"/>
-      <c r="D55" s="89"/>
-      <c r="E55" s="89"/>
-      <c r="F55" s="90"/>
-      <c r="G55" s="89"/>
-      <c r="H55" s="91"/>
-      <c r="I55" s="97"/>
-      <c r="J55" s="98"/>
+      <c r="A55" s="90"/>
+      <c r="B55" s="90"/>
+      <c r="C55" s="90"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="91"/>
+      <c r="G55" s="90"/>
+      <c r="H55" s="92"/>
+      <c r="I55" s="98"/>
+      <c r="J55" s="99"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
     </row>
     <row r="56" ht="21.0" customHeight="1">
-      <c r="A56" s="89"/>
-      <c r="B56" s="89"/>
-      <c r="C56" s="89"/>
-      <c r="D56" s="89"/>
-      <c r="E56" s="89"/>
-      <c r="F56" s="90"/>
-      <c r="G56" s="89"/>
-      <c r="H56" s="91"/>
-      <c r="I56" s="94"/>
-      <c r="J56" s="95"/>
+      <c r="A56" s="90"/>
+      <c r="B56" s="90"/>
+      <c r="C56" s="90"/>
+      <c r="D56" s="90"/>
+      <c r="E56" s="90"/>
+      <c r="F56" s="91"/>
+      <c r="G56" s="90"/>
+      <c r="H56" s="92"/>
+      <c r="I56" s="95"/>
+      <c r="J56" s="96"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
     </row>
     <row r="57" ht="21.0" customHeight="1">
-      <c r="A57" s="89"/>
-      <c r="B57" s="89"/>
-      <c r="C57" s="89"/>
-      <c r="D57" s="89"/>
-      <c r="E57" s="89"/>
-      <c r="F57" s="90"/>
-      <c r="G57" s="89"/>
-      <c r="H57" s="91"/>
-      <c r="I57" s="94"/>
-      <c r="J57" s="95"/>
+      <c r="A57" s="90"/>
+      <c r="B57" s="90"/>
+      <c r="C57" s="90"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="90"/>
+      <c r="F57" s="91"/>
+      <c r="G57" s="90"/>
+      <c r="H57" s="92"/>
+      <c r="I57" s="95"/>
+      <c r="J57" s="96"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
     </row>
     <row r="58" ht="21.0" customHeight="1">
-      <c r="A58" s="89"/>
-      <c r="B58" s="89"/>
-      <c r="C58" s="89"/>
-      <c r="D58" s="89"/>
-      <c r="E58" s="89"/>
-      <c r="F58" s="90"/>
-      <c r="G58" s="89"/>
-      <c r="H58" s="91"/>
-      <c r="I58" s="96"/>
-      <c r="J58" s="95"/>
+      <c r="A58" s="90"/>
+      <c r="B58" s="90"/>
+      <c r="C58" s="90"/>
+      <c r="D58" s="90"/>
+      <c r="E58" s="90"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="90"/>
+      <c r="H58" s="92"/>
+      <c r="I58" s="97"/>
+      <c r="J58" s="96"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
     </row>
     <row r="59" ht="21.0" customHeight="1">
-      <c r="A59" s="89"/>
-      <c r="B59" s="89"/>
-      <c r="C59" s="89"/>
-      <c r="D59" s="89"/>
-      <c r="E59" s="89"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="89"/>
-      <c r="H59" s="91"/>
-      <c r="I59" s="97"/>
-      <c r="J59" s="98"/>
+      <c r="A59" s="90"/>
+      <c r="B59" s="90"/>
+      <c r="C59" s="90"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="91"/>
+      <c r="G59" s="90"/>
+      <c r="H59" s="92"/>
+      <c r="I59" s="98"/>
+      <c r="J59" s="99"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
     </row>
     <row r="60" ht="21.0" customHeight="1">
-      <c r="A60" s="89"/>
-      <c r="B60" s="89"/>
-      <c r="C60" s="89"/>
-      <c r="D60" s="89"/>
-      <c r="E60" s="89"/>
-      <c r="F60" s="90"/>
-      <c r="G60" s="89"/>
-      <c r="H60" s="91"/>
-      <c r="I60" s="94"/>
-      <c r="J60" s="95"/>
+      <c r="A60" s="90"/>
+      <c r="B60" s="90"/>
+      <c r="C60" s="90"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="90"/>
+      <c r="H60" s="92"/>
+      <c r="I60" s="95"/>
+      <c r="J60" s="96"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
     </row>
     <row r="61" ht="21.0" customHeight="1">
-      <c r="A61" s="89"/>
-      <c r="B61" s="89"/>
-      <c r="C61" s="89"/>
-      <c r="D61" s="89"/>
-      <c r="E61" s="89"/>
-      <c r="F61" s="90"/>
-      <c r="G61" s="89"/>
-      <c r="H61" s="91"/>
-      <c r="I61" s="94"/>
-      <c r="J61" s="95"/>
+      <c r="A61" s="90"/>
+      <c r="B61" s="90"/>
+      <c r="C61" s="90"/>
+      <c r="D61" s="90"/>
+      <c r="E61" s="90"/>
+      <c r="F61" s="91"/>
+      <c r="G61" s="90"/>
+      <c r="H61" s="92"/>
+      <c r="I61" s="95"/>
+      <c r="J61" s="96"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
     </row>
     <row r="62" ht="21.0" customHeight="1">
-      <c r="A62" s="89"/>
-      <c r="B62" s="89"/>
-      <c r="C62" s="89"/>
-      <c r="D62" s="89"/>
-      <c r="E62" s="89"/>
-      <c r="F62" s="90"/>
-      <c r="G62" s="89"/>
-      <c r="H62" s="91"/>
-      <c r="I62" s="96"/>
-      <c r="J62" s="95"/>
+      <c r="A62" s="90"/>
+      <c r="B62" s="90"/>
+      <c r="C62" s="90"/>
+      <c r="D62" s="90"/>
+      <c r="E62" s="90"/>
+      <c r="F62" s="91"/>
+      <c r="G62" s="90"/>
+      <c r="H62" s="92"/>
+      <c r="I62" s="97"/>
+      <c r="J62" s="96"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
     </row>
     <row r="63" ht="21.0" customHeight="1">
-      <c r="A63" s="89"/>
-      <c r="B63" s="89"/>
-      <c r="C63" s="89"/>
-      <c r="D63" s="89"/>
-      <c r="E63" s="89"/>
-      <c r="F63" s="90"/>
-      <c r="G63" s="89"/>
-      <c r="H63" s="91"/>
-      <c r="I63" s="97"/>
-      <c r="J63" s="98"/>
+      <c r="A63" s="90"/>
+      <c r="B63" s="90"/>
+      <c r="C63" s="90"/>
+      <c r="D63" s="90"/>
+      <c r="E63" s="90"/>
+      <c r="F63" s="91"/>
+      <c r="G63" s="90"/>
+      <c r="H63" s="92"/>
+      <c r="I63" s="98"/>
+      <c r="J63" s="99"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
     </row>
     <row r="64" ht="21.0" customHeight="1">
-      <c r="A64" s="89"/>
-      <c r="B64" s="89"/>
-      <c r="C64" s="89"/>
-      <c r="D64" s="89"/>
-      <c r="E64" s="89"/>
-      <c r="F64" s="90"/>
-      <c r="G64" s="89"/>
-      <c r="H64" s="91"/>
-      <c r="I64" s="94"/>
-      <c r="J64" s="95"/>
+      <c r="A64" s="90"/>
+      <c r="B64" s="90"/>
+      <c r="C64" s="90"/>
+      <c r="D64" s="90"/>
+      <c r="E64" s="90"/>
+      <c r="F64" s="91"/>
+      <c r="G64" s="90"/>
+      <c r="H64" s="92"/>
+      <c r="I64" s="95"/>
+      <c r="J64" s="96"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
     </row>
     <row r="65" ht="21.0" customHeight="1">
-      <c r="A65" s="89"/>
-      <c r="B65" s="89"/>
-      <c r="C65" s="89"/>
-      <c r="D65" s="89"/>
-      <c r="E65" s="89"/>
-      <c r="F65" s="90"/>
-      <c r="G65" s="89"/>
-      <c r="H65" s="91"/>
-      <c r="I65" s="94"/>
-      <c r="J65" s="95"/>
+      <c r="A65" s="90"/>
+      <c r="B65" s="90"/>
+      <c r="C65" s="90"/>
+      <c r="D65" s="90"/>
+      <c r="E65" s="90"/>
+      <c r="F65" s="91"/>
+      <c r="G65" s="90"/>
+      <c r="H65" s="92"/>
+      <c r="I65" s="95"/>
+      <c r="J65" s="96"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
     </row>
     <row r="66" ht="21.0" customHeight="1">
-      <c r="A66" s="89"/>
-      <c r="B66" s="89"/>
-      <c r="C66" s="89"/>
-      <c r="D66" s="89"/>
-      <c r="E66" s="89"/>
-      <c r="F66" s="90"/>
-      <c r="G66" s="89"/>
-      <c r="H66" s="91"/>
-      <c r="I66" s="96"/>
-      <c r="J66" s="95"/>
+      <c r="A66" s="90"/>
+      <c r="B66" s="90"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="90"/>
+      <c r="E66" s="90"/>
+      <c r="F66" s="91"/>
+      <c r="G66" s="90"/>
+      <c r="H66" s="92"/>
+      <c r="I66" s="97"/>
+      <c r="J66" s="96"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
     </row>
@@ -2343,11 +2347,11 @@
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
-      <c r="H70" s="99" t="s">
-        <v>40</v>
-      </c>
-      <c r="I70" s="100"/>
-      <c r="J70" s="101">
+      <c r="H70" s="100" t="s">
+        <v>41</v>
+      </c>
+      <c r="I70" s="101"/>
+      <c r="J70" s="102">
         <f>SUM((J21+J28)-J44-J67)</f>
         <v>0</v>
       </c>
@@ -2396,20 +2400,6 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" ht="21.0" customHeight="1">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C13:D13"/>
